--- a/data/env_test/case_excle/GovermentPurcharsWT/case_data_zz.xlsx
+++ b/data/env_test/case_excle/GovermentPurcharsWT/case_data_zz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Lucas/PycharmProjects/InterfaceAutomaticTesttPlatform/data/env_test/case_excle/GovermentPurcharsWT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE4A1C8-DEE6-E74B-ACFC-38094031B0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBC68DB-F7E1-E145-98E3-250BC5688A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36000" yWindow="500" windowWidth="51200" windowHeight="28300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="19380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="公开" sheetId="10" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="184">
   <si>
     <t>编号</t>
   </si>
@@ -635,6 +635,34 @@
   <si>
     <t>{"paName":"$.data.name","paCode":"$.data.ecode"}</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>a20</t>
+  </si>
+  <si>
+    <t>a25</t>
+  </si>
+  <si>
+    <t>a26</t>
+  </si>
+  <si>
+    <t>{"tenderProName":"${purchaseProjectName}","tenderProCode":"${purchaseProjectCode}","gpBudget":"2344万元","limitedPrice":"344万元","getDocAddr":"沙河市阳光招采平台（http://www.jy.jiezhaowang.com）","submitAddr":"测试","projectContact":"测试","projectContactTel":"13000000001","tfPrice":"200元","ifSyndicatedFlag":0,"ifSyndicatedFlagCus":"拒绝","noticeName":"测试","purchaseContent":"测试","supplierQualification":"测试","contractTerm":"测试","spSupplierQualification":"测试","docGetStartTime":"${noticeSendTime}","docGetStartTimeCus":"${noticeSendTime}","docGetEndTime":"${noticeEndTime}","docGetEndTimeCus":"${noticeEndTime}","startMor":"00:11:08","startMorCus":"00:11:08","endMor":"12:00:00","endMorCus":"12:00:00","startAfter":"12:11:20","startAfterCus":"12:11:20","endAfter":"23:11:26","endAfterCus":"23:11:26","tenderDocGetMethodStr":"测试","bidOpenTime":"${noticeEndTime}","bidOpenTimeCus":"${noticeEndTime}","bidDocReferEndTime":"${noticeEndTime}","bidDocReferEndTimeCus":"${noticeEndTime}","bidOpenAddr":"测试","remark":"测试","collectName":"测试","collectPersonAddr":"测试","collectPersonTel":"13000000001","openType":0,"bulletinMediaCus":["1722594868247506946"],"noticeNature":0,"tenderProType":"1","tenderProId":"${tpId}","bidMode":"${purchaseMode}","bulletinType":4,"sectionType":2,"regionName":"河北省-唐山市-路北区","regionCode":"130203","challengeCall":"13000000001","tenderDocGetMethod":1,"sectionIds":"${bidSectionId}","bulletinMedia":"1722594868247506946","agencyFullName":"测试","agencyAddr":"测试","agencyContactTel":"13000000001","hostId":"${hostId}","hostName":"${hostName}","hostTelephone":"13085840000","hostOrgId":"${hostOrgId}","noticeTime":["${noticeSendTime}","${noticeEndTime}"],"bidDocReferMethod":"1","sectionList":[{"id":"${bidSectionId}","bidSectionCode":"${bidSectionCode}","bidSectionName":"${bidSectionName}","addedNum":0,"ifChecked":"true","bidOpenTime":"","bidLimitPriceHighest":"344","tfPrice":"200","bidLimitPriceUnit":1,"investBudget":"","ifSyndicatedFlag":"false"}],"sectionListCus":[{"id":"${bidSectionId}","bidSectionCode":"${bidSectionCode}","bidSectionName":"${bidSectionName}","addedNum":0,"ifChecked":"true","bidOpenTime":"","bidLimitPriceHighest":"344","tfPrice":"200","bidLimitPriceUnit":1,"investBudget":"","ifSyndicatedFlag":"false"}],"noticeSendTime":"${noticeSendTime}","noticeEndTime":"${noticeEndTime}","noticeContent":"&lt;div data-v-148f4874=\"\" id=\"editorContent\" style=\"overflow-wrap: break-word; word-break: break-all; font-family: 微软雅黑;\"&gt;&lt;h3 data-v-148f4874=\"\" style=\"text-align: center;\"&gt;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/h3&gt; &lt;h4 data-v-148f4874=\"\"&gt;项目概况&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;${purchaseProjectName}&lt;/span&gt; 招标项目的潜在投标人应在&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt; 获取招标文件，并于&amp;nbsp;&lt;span data-v-148f4874=\"\"&gt;${noticeEndTime}&lt;/span&gt;&amp;nbsp;前递交投标文件。&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;一、项目基本情况&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;项目编号： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;${tpId}&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;项目名称：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;${purchaseProjectName}&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;预算金额： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;2344万元&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;最高限价： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;344万元&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&lt;span data-v-148f4874=\"\" style=\"font-family: SimHei, sans-serif;\"&gt;&lt;span data-v-148f4874=\"\" style=\"font-family: &amp;quot;Microsoft YaHei&amp;quot;, &amp;quot;Helvetica Neue&amp;quot;, &amp;quot;PingFang SC&amp;quot;, sans-serif;\"&gt;采购需求： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&lt;span data-v-148f4874=\"\" style=\"font-family: &amp;quot;Microsoft YaHei&amp;quot;, &amp;quot;Helvetica Neue&amp;quot;, &amp;quot;PingFang SC&amp;quot;, sans-serif;\"&gt;合同履行期限：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/span&gt;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;本项目&amp;nbsp;&lt;span data-v-148f4874=\"\"&gt;拒绝&lt;/span&gt; 联合体投标&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;二、申请人的资格要求&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;1、法律规定：满足《中华人民共和国政府采购法》第二十二条规定;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;2、落实政府采购政策需满足的资格要求：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;3、本项目的特定要求：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;三、获取招标文件&lt;/h4&gt; &lt;p data-v-148f4874=\"\" style=\"line-height: 2;\"&gt;时间：&lt;span data-v-148f4874=\"\"&gt;${noticeSendTime}&lt;/span&gt;&amp;nbsp; 至 &lt;span data-v-148f4874=\"\"&gt;${noticeEndTime}&lt;/span&gt;&amp;nbsp;，每天上午 &lt;span data-v-148f4874=\"\"&gt;00:11:08&lt;/span&gt;&amp;nbsp;- &lt;span data-v-148f4874=\"\"&gt;12:00:00&lt;/span&gt;&amp;nbsp;，下午 &lt;span data-v-148f4874=\"\"&gt;12:11:20&lt;/span&gt;&amp;nbsp;- &lt;span data-v-148f4874=\"\"&gt;23:11:26&lt;/span&gt;&amp;nbsp;（北京时间，法定节假日除外）&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;地点：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;沙河市阳光招采平台（http://www.jy.jiezhaowang.com）&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;方式:&amp;nbsp; &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;售价：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;200元&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;四、响应文件提交&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;截止时间：&lt;span data-v-148f4874=\"\"&gt;${noticeEndTime}&lt;/span&gt;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;地点：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;五、开启&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;时间：&amp;nbsp;&lt;span data-v-148f4874=\"\"&gt;${noticeEndTime}&lt;/span&gt;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;地点：&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;公告期限&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;自本公告发布之日起5个工作日。&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;六、其他补充事项&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;七、对本次招标提出询问，请按以下方式联系&lt;/h4&gt; &lt;p data-v-148f4874=\"\"&gt;1.采购人信息&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp; 名&amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp;称： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp; 地&amp;nbsp; &amp;nbsp; &amp;nbsp; &amp;nbsp;址：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt; &amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp; 联系方式：&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;13000000001&lt;/span&gt;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;2.项目联系方式&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp; 项目负责人： &lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;测试&lt;/span&gt;&amp;nbsp;&lt;/p&gt; &lt;p data-v-148f4874=\"\"&gt;&amp;nbsp; 联 系 方 式：&amp;nbsp;&lt;span data-v-148f4874=\"\" class=\"textUnderline\"&gt;13000000001&lt;/span&gt;&lt;/p&gt; &lt;h4 data-v-148f4874=\"\"&gt;&amp;nbsp;&lt;/h4&gt;&lt;/div&gt;","templateDetailId":"1879804151350157313"}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取当前用户信息</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>etbtrade/tenderBulletin/getUserList</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"hostId":"$.data[0].userId","hostName":"$.data[0].name","hostOrgId":"$.data[0].orgCode"}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>a27</t>
   </si>
 </sst>
 </file>
@@ -739,7 +767,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -771,11 +799,69 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFD84472"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC80000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC4E59F"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF00B853"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1229,7 +1315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1321,6 +1407,9 @@
       </c>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="B3" s="10" t="s">
         <v>161</v>
       </c>
@@ -1350,6 +1439,9 @@
       </c>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="B4" s="10" t="s">
         <v>163</v>
       </c>
@@ -1379,6 +1471,9 @@
       </c>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="B5" s="10" t="s">
         <v>165</v>
       </c>
@@ -1409,7 +1504,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>56</v>
@@ -1441,7 +1536,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>57</v>
@@ -1473,7 +1568,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>60</v>
@@ -1502,7 +1597,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>97</v>
@@ -1531,7 +1626,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>44</v>
@@ -1563,7 +1658,7 @@
     </row>
     <row r="11" spans="1:14" ht="360">
       <c r="A11" s="1" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>26</v>
@@ -1596,7 +1691,7 @@
     </row>
     <row r="12" spans="1:14" ht="126">
       <c r="A12" s="1" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>109</v>
@@ -1627,7 +1722,7 @@
     </row>
     <row r="13" spans="1:14" ht="90">
       <c r="A13" s="1" t="s">
-        <v>99</v>
+        <v>30</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>105</v>
@@ -1661,7 +1756,7 @@
     </row>
     <row r="14" spans="1:14" ht="409.6">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>29</v>
@@ -1690,7 +1785,7 @@
     </row>
     <row r="15" spans="1:14" ht="252">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>93</v>
@@ -1725,7 +1820,7 @@
     </row>
     <row r="16" spans="1:14" ht="90">
       <c r="A16" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>32</v>
@@ -1754,7 +1849,7 @@
     </row>
     <row r="17" spans="1:14" ht="90">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>79</v>
@@ -1783,7 +1878,7 @@
     </row>
     <row r="18" spans="1:14" ht="90">
       <c r="A18" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>81</v>
@@ -1812,7 +1907,7 @@
     </row>
     <row r="19" spans="1:14" ht="90">
       <c r="A19" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>83</v>
@@ -1841,7 +1936,7 @@
     </row>
     <row r="20" spans="1:14" ht="90">
       <c r="A20" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>84</v>
@@ -1870,7 +1965,7 @@
     </row>
     <row r="21" spans="1:14" ht="90">
       <c r="A21" s="1" t="s">
-        <v>38</v>
+        <v>176</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>85</v>
@@ -1899,7 +1994,7 @@
     </row>
     <row r="22" spans="1:14" ht="90">
       <c r="A22" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>86</v>
@@ -1928,7 +2023,7 @@
     </row>
     <row r="23" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>95</v>
@@ -1955,167 +2050,217 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="409.6">
+    <row r="24" spans="1:14" s="10" customFormat="1" ht="102.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="14"/>
+      <c r="J24" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="409.6">
+      <c r="A25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="90">
-      <c r="A25" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="90">
+      <c r="A26" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1" t="s">
+      <c r="E26" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1" t="s">
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="L25" s="1"/>
-      <c r="M25" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
-      <c r="A26" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B26" s="1" t="s">
+      <c r="L26" s="1"/>
+      <c r="M26" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
+      <c r="A27" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" s="1" t="s">
+      <c r="E27" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="1" t="s">
+      <c r="H27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="M26" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="N26" s="1">
+      <c r="M27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N27" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="90">
-      <c r="A27" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="1" t="s">
+    <row r="28" spans="1:14" ht="90">
+      <c r="A28" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C28" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" s="1" t="s">
+      <c r="E28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="1" t="s">
+      <c r="H28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M27" s="5" t="s">
+      <c r="M28" s="5" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="E2:E27">
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
+  <conditionalFormatting sqref="E2:E23 E25:E28">
+    <cfRule type="cellIs" dxfId="19" priority="11" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="12" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="13" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="14" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="15" operator="equal">
+      <formula>"P1"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E24">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"P5"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"P4"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"P3"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+      <formula>"P2"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WVM23 WLQ23 WBU23 VRY23 VIC23 UYG23 UOK23 UEO23 TUS23 TKW23 TBA23 SRE23 SHI23 RXM23 RNQ23 RDU23 QTY23 QKC23 QAG23 PQK23 PGO23 OWS23 OMW23 ODA23 NTE23 NJI23 MZM23 MPQ23 MFU23 LVY23 LMC23 LCG23 KSK23 KIO23 JYS23 JOW23 JFA23 IVE23 ILI23 IBM23 HRQ23 HHU23 GXY23 GOC23 GEG23 FUK23 FKO23 FAS23 EQW23 EHA23 DXE23 DNI23 DDM23 CTQ23 CJU23 BZY23 BQC23 BGG23 AWK23 AMO23 ACS23 SW23 JA23 WVM26 WLQ26 WBU26 VRY26 VIC26 UYG26 UOK26 UEO26 TUS26 TKW26 TBA26 SRE26 SHI26 RXM26 RNQ26 RDU26 QTY26 QKC26 QAG26 PQK26 PGO26 OWS26 OMW26 ODA26 NTE26 NJI26 MZM26 MPQ26 MFU26 LVY26 LMC26 LCG26 KSK26 KIO26 JYS26 JOW26 JFA26 IVE26 ILI26 IBM26 HRQ26 HHU26 GXY26 GOC26 GEG26 FUK26 FKO26 FAS26 EQW26 EHA26 DXE26 DNI26 DDM26 CTQ26 CJU26 BZY26 BQC26 BGG26 AWK26 AMO26 ACS26 SW26 JA26 SW1:SW10 ACS1:ACS10 AMO1:AMO10 AWK1:AWK10 BGG1:BGG10 BQC1:BQC10 BZY1:BZY10 CJU1:CJU10 CTQ1:CTQ10 DDM1:DDM10 DNI1:DNI10 DXE1:DXE10 EHA1:EHA10 EQW1:EQW10 FAS1:FAS10 FKO1:FKO10 FUK1:FUK10 GEG1:GEG10 GOC1:GOC10 GXY1:GXY10 HHU1:HHU10 HRQ1:HRQ10 IBM1:IBM10 ILI1:ILI10 IVE1:IVE10 JFA1:JFA10 JOW1:JOW10 JYS1:JYS10 KIO1:KIO10 KSK1:KSK10 LCG1:LCG10 LMC1:LMC10 LVY1:LVY10 MFU1:MFU10 MPQ1:MPQ10 MZM1:MZM10 NJI1:NJI10 NTE1:NTE10 ODA1:ODA10 OMW1:OMW10 OWS1:OWS10 PGO1:PGO10 PQK1:PQK10 QAG1:QAG10 QKC1:QKC10 QTY1:QTY10 RDU1:RDU10 RNQ1:RNQ10 RXM1:RXM10 SHI1:SHI10 SRE1:SRE10 TBA1:TBA10 TKW1:TKW10 TUS1:TUS10 UEO1:UEO10 UOK1:UOK10 UYG1:UYG10 VIC1:VIC10 VRY1:VRY10 WBU1:WBU10 WLQ1:WLQ10 WVM1:WVM10 JA1:JA10" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WLQ23:WLQ24 WBU23:WBU24 VRY23:VRY24 VIC23:VIC24 UYG23:UYG24 UOK23:UOK24 UEO23:UEO24 TUS23:TUS24 TKW23:TKW24 TBA23:TBA24 SRE23:SRE24 SHI23:SHI24 RXM23:RXM24 RNQ23:RNQ24 RDU23:RDU24 QTY23:QTY24 QKC23:QKC24 QAG23:QAG24 PQK23:PQK24 PGO23:PGO24 OWS23:OWS24 OMW23:OMW24 ODA23:ODA24 NTE23:NTE24 NJI23:NJI24 MZM23:MZM24 MPQ23:MPQ24 MFU23:MFU24 LVY23:LVY24 LMC23:LMC24 LCG23:LCG24 KSK23:KSK24 KIO23:KIO24 JYS23:JYS24 JOW23:JOW24 JFA23:JFA24 IVE23:IVE24 ILI23:ILI24 IBM23:IBM24 HRQ23:HRQ24 HHU23:HHU24 GXY23:GXY24 GOC23:GOC24 GEG23:GEG24 FUK23:FUK24 FKO23:FKO24 FAS23:FAS24 EQW23:EQW24 EHA23:EHA24 DXE23:DXE24 DNI23:DNI24 DDM23:DDM24 CTQ23:CTQ24 CJU23:CJU24 BZY23:BZY24 BQC23:BQC24 BGG23:BGG24 AWK23:AWK24 AMO23:AMO24 ACS23:ACS24 SW23:SW24 JA23:JA24 JA1:JA10 WVM27 WLQ27 WBU27 VRY27 VIC27 UYG27 UOK27 UEO27 TUS27 TKW27 TBA27 SRE27 SHI27 RXM27 RNQ27 RDU27 QTY27 QKC27 QAG27 PQK27 PGO27 OWS27 OMW27 ODA27 NTE27 NJI27 MZM27 MPQ27 MFU27 LVY27 LMC27 LCG27 KSK27 KIO27 JYS27 JOW27 JFA27 IVE27 ILI27 IBM27 HRQ27 HHU27 GXY27 GOC27 GEG27 FUK27 FKO27 FAS27 EQW27 EHA27 DXE27 DNI27 DDM27 CTQ27 CJU27 BZY27 BQC27 BGG27 AWK27 AMO27 ACS27 SW27 JA27 SW1:SW10 ACS1:ACS10 AMO1:AMO10 AWK1:AWK10 BGG1:BGG10 BQC1:BQC10 BZY1:BZY10 CJU1:CJU10 CTQ1:CTQ10 DDM1:DDM10 DNI1:DNI10 DXE1:DXE10 EHA1:EHA10 EQW1:EQW10 FAS1:FAS10 FKO1:FKO10 FUK1:FUK10 GEG1:GEG10 GOC1:GOC10 GXY1:GXY10 HHU1:HHU10 HRQ1:HRQ10 IBM1:IBM10 ILI1:ILI10 IVE1:IVE10 JFA1:JFA10 JOW1:JOW10 JYS1:JYS10 KIO1:KIO10 KSK1:KSK10 LCG1:LCG10 LMC1:LMC10 LVY1:LVY10 MFU1:MFU10 MPQ1:MPQ10 MZM1:MZM10 NJI1:NJI10 NTE1:NTE10 ODA1:ODA10 OMW1:OMW10 OWS1:OWS10 PGO1:PGO10 PQK1:PQK10 QAG1:QAG10 QKC1:QKC10 QTY1:QTY10 RDU1:RDU10 RNQ1:RNQ10 RXM1:RXM10 SHI1:SHI10 SRE1:SRE10 TBA1:TBA10 TKW1:TKW10 TUS1:TUS10 UEO1:UEO10 UOK1:UOK10 UYG1:UYG10 VIC1:VIC10 VRY1:VRY10 WBU1:WBU10 WLQ1:WLQ10 WVM1:WVM10 WVM23:WVM24" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WVN23 WLR23 WBV23 VRZ23 VID23 UYH23 UOL23 UEP23 TUT23 TKX23 TBB23 SRF23 SHJ23 RXN23 RNR23 RDV23 QTZ23 QKD23 QAH23 PQL23 PGP23 OWT23 OMX23 ODB23 NTF23 NJJ23 MZN23 MPR23 MFV23 LVZ23 LMD23 LCH23 KSL23 KIP23 JYT23 JOX23 JFB23 IVF23 ILJ23 IBN23 HRR23 HHV23 GXZ23 GOD23 GEH23 FUL23 FKP23 FAT23 EQX23 EHB23 DXF23 DNJ23 DDN23 CTR23 CJV23 BZZ23 BQD23 BGH23 AWL23 AMP23 ACT23 SX23 JB23 WVN26 WLR26 WBV26 VRZ26 VID26 UYH26 UOL26 UEP26 TUT26 TKX26 TBB26 SRF26 SHJ26 RXN26 RNR26 RDV26 QTZ26 QKD26 QAH26 PQL26 PGP26 OWT26 OMX26 ODB26 NTF26 NJJ26 MZN26 MPR26 MFV26 LVZ26 LMD26 LCH26 KSL26 KIP26 JYT26 JOX26 JFB26 IVF26 ILJ26 IBN26 HRR26 HHV26 GXZ26 GOD26 GEH26 FUL26 FKP26 FAT26 EQX26 EHB26 DXF26 DNJ26 DDN26 CTR26 CJV26 BZZ26 BQD26 BGH26 AWL26 AMP26 ACT26 SX26 JB26 G1:G27 JB1:JB10 SX1:SX10 ACT1:ACT10 AMP1:AMP10 AWL1:AWL10 BGH1:BGH10 BQD1:BQD10 BZZ1:BZZ10 CJV1:CJV10 CTR1:CTR10 DDN1:DDN10 DNJ1:DNJ10 DXF1:DXF10 EHB1:EHB10 EQX1:EQX10 FAT1:FAT10 FKP1:FKP10 FUL1:FUL10 GEH1:GEH10 GOD1:GOD10 GXZ1:GXZ10 HHV1:HHV10 HRR1:HRR10 IBN1:IBN10 ILJ1:ILJ10 IVF1:IVF10 JFB1:JFB10 JOX1:JOX10 JYT1:JYT10 KIP1:KIP10 KSL1:KSL10 LCH1:LCH10 LMD1:LMD10 LVZ1:LVZ10 MFV1:MFV10 MPR1:MPR10 MZN1:MZN10 NJJ1:NJJ10 NTF1:NTF10 ODB1:ODB10 OMX1:OMX10 OWT1:OWT10 PGP1:PGP10 PQL1:PQL10 QAH1:QAH10 QKD1:QKD10 QTZ1:QTZ10 RDV1:RDV10 RNR1:RNR10 RXN1:RXN10 SHJ1:SHJ10 SRF1:SRF10 TBB1:TBB10 TKX1:TKX10 TUT1:TUT10 UEP1:UEP10 UOL1:UOL10 UYH1:UYH10 VID1:VID10 VRZ1:VRZ10 WBV1:WBV10 WLR1:WLR10 WVN1:WVN10" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WLR23:WLR24 WBV23:WBV24 VRZ23:VRZ24 VID23:VID24 UYH23:UYH24 UOL23:UOL24 UEP23:UEP24 TUT23:TUT24 TKX23:TKX24 TBB23:TBB24 SRF23:SRF24 SHJ23:SHJ24 RXN23:RXN24 RNR23:RNR24 RDV23:RDV24 QTZ23:QTZ24 QKD23:QKD24 QAH23:QAH24 PQL23:PQL24 PGP23:PGP24 OWT23:OWT24 OMX23:OMX24 ODB23:ODB24 NTF23:NTF24 NJJ23:NJJ24 MZN23:MZN24 MPR23:MPR24 MFV23:MFV24 LVZ23:LVZ24 LMD23:LMD24 LCH23:LCH24 KSL23:KSL24 KIP23:KIP24 JYT23:JYT24 JOX23:JOX24 JFB23:JFB24 IVF23:IVF24 ILJ23:ILJ24 IBN23:IBN24 HRR23:HRR24 HHV23:HHV24 GXZ23:GXZ24 GOD23:GOD24 GEH23:GEH24 FUL23:FUL24 FKP23:FKP24 FAT23:FAT24 EQX23:EQX24 EHB23:EHB24 DXF23:DXF24 DNJ23:DNJ24 DDN23:DDN24 CTR23:CTR24 CJV23:CJV24 BZZ23:BZZ24 BQD23:BQD24 BGH23:BGH24 AWL23:AWL24 AMP23:AMP24 ACT23:ACT24 SX23:SX24 JB23:JB24 WVN27 WLR27 WBV27 VRZ27 VID27 UYH27 UOL27 UEP27 TUT27 TKX27 TBB27 SRF27 SHJ27 RXN27 RNR27 RDV27 QTZ27 QKD27 QAH27 PQL27 PGP27 OWT27 OMX27 ODB27 NTF27 NJJ27 MZN27 MPR27 MFV27 LVZ27 LMD27 LCH27 KSL27 KIP27 JYT27 JOX27 JFB27 IVF27 ILJ27 IBN27 HRR27 HHV27 GXZ27 GOD27 GEH27 FUL27 FKP27 FAT27 EQX27 EHB27 DXF27 DNJ27 DDN27 CTR27 CJV27 BZZ27 BQD27 BGH27 AWL27 AMP27 ACT27 SX27 JB27 WVN1:WVN10 JB1:JB10 SX1:SX10 ACT1:ACT10 AMP1:AMP10 AWL1:AWL10 BGH1:BGH10 BQD1:BQD10 BZZ1:BZZ10 CJV1:CJV10 CTR1:CTR10 DDN1:DDN10 DNJ1:DNJ10 DXF1:DXF10 EHB1:EHB10 EQX1:EQX10 FAT1:FAT10 FKP1:FKP10 FUL1:FUL10 GEH1:GEH10 GOD1:GOD10 GXZ1:GXZ10 HHV1:HHV10 HRR1:HRR10 IBN1:IBN10 ILJ1:ILJ10 IVF1:IVF10 JFB1:JFB10 JOX1:JOX10 JYT1:JYT10 KIP1:KIP10 KSL1:KSL10 LCH1:LCH10 LMD1:LMD10 LVZ1:LVZ10 MFV1:MFV10 MPR1:MPR10 MZN1:MZN10 NJJ1:NJJ10 NTF1:NTF10 ODB1:ODB10 OMX1:OMX10 OWT1:OWT10 PGP1:PGP10 PQL1:PQL10 QAH1:QAH10 QKD1:QKD10 QTZ1:QTZ10 RDV1:RDV10 RNR1:RNR10 RXN1:RXN10 SHJ1:SHJ10 SRF1:SRF10 TBB1:TBB10 TKX1:TKX10 TUT1:TUT10 UEP1:UEP10 UOL1:UOL10 UYH1:UYH10 VID1:VID10 VRZ1:VRZ10 WBV1:WBV10 WLR1:WLR10 G1:G28 WVN23:WVN24" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"get,post,put,delete,head,options,patch"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WVO23 WLS23 WBW23 VSA23 VIE23 UYI23 UOM23 UEQ23 TUU23 TKY23 TBC23 SRG23 SHK23 RXO23 RNS23 RDW23 QUA23 QKE23 QAI23 PQM23 PGQ23 OWU23 OMY23 ODC23 NTG23 NJK23 MZO23 MPS23 MFW23 LWA23 LME23 LCI23 KSM23 KIQ23 JYU23 JOY23 JFC23 IVG23 ILK23 IBO23 HRS23 HHW23 GYA23 GOE23 GEI23 FUM23 FKQ23 FAU23 EQY23 EHC23 DXG23 DNK23 DDO23 CTS23 CJW23 CAA23 BQE23 BGI23 AWM23 AMQ23 ACU23 SY23 JC23 WVO26 WLS26 WBW26 VSA26 VIE26 UYI26 UOM26 UEQ26 TUU26 TKY26 TBC26 SRG26 SHK26 RXO26 RNS26 RDW26 QUA26 QKE26 QAI26 PQM26 PGQ26 OWU26 OMY26 ODC26 NTG26 NJK26 MZO26 MPS26 MFW26 LWA26 LME26 LCI26 KSM26 KIQ26 JYU26 JOY26 JFC26 IVG26 ILK26 IBO26 HRS26 HHW26 GYA26 GOE26 GEI26 FUM26 FKQ26 FAU26 EQY26 EHC26 DXG26 DNK26 DDO26 CTS26 CJW26 CAA26 BQE26 BGI26 AWM26 AMQ26 ACU26 SY26 JC26 H1:H27 JC1:JC10 SY1:SY10 ACU1:ACU10 AMQ1:AMQ10 AWM1:AWM10 BGI1:BGI10 BQE1:BQE10 CAA1:CAA10 CJW1:CJW10 CTS1:CTS10 DDO1:DDO10 DNK1:DNK10 DXG1:DXG10 EHC1:EHC10 EQY1:EQY10 FAU1:FAU10 FKQ1:FKQ10 FUM1:FUM10 GEI1:GEI10 GOE1:GOE10 GYA1:GYA10 HHW1:HHW10 HRS1:HRS10 IBO1:IBO10 ILK1:ILK10 IVG1:IVG10 JFC1:JFC10 JOY1:JOY10 JYU1:JYU10 KIQ1:KIQ10 KSM1:KSM10 LCI1:LCI10 LME1:LME10 LWA1:LWA10 MFW1:MFW10 MPS1:MPS10 MZO1:MZO10 NJK1:NJK10 NTG1:NTG10 ODC1:ODC10 OMY1:OMY10 OWU1:OWU10 PGQ1:PGQ10 PQM1:PQM10 QAI1:QAI10 QKE1:QKE10 QUA1:QUA10 RDW1:RDW10 RNS1:RNS10 RXO1:RXO10 SHK1:SHK10 SRG1:SRG10 TBC1:TBC10 TKY1:TKY10 TUU1:TUU10 UEQ1:UEQ10 UOM1:UOM10 UYI1:UYI10 VIE1:VIE10 VSA1:VSA10 WBW1:WBW10 WLS1:WLS10 WVO1:WVO10" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="WLS23:WLS24 WBW23:WBW24 VSA23:VSA24 VIE23:VIE24 UYI23:UYI24 UOM23:UOM24 UEQ23:UEQ24 TUU23:TUU24 TKY23:TKY24 TBC23:TBC24 SRG23:SRG24 SHK23:SHK24 RXO23:RXO24 RNS23:RNS24 RDW23:RDW24 QUA23:QUA24 QKE23:QKE24 QAI23:QAI24 PQM23:PQM24 PGQ23:PGQ24 OWU23:OWU24 OMY23:OMY24 ODC23:ODC24 NTG23:NTG24 NJK23:NJK24 MZO23:MZO24 MPS23:MPS24 MFW23:MFW24 LWA23:LWA24 LME23:LME24 LCI23:LCI24 KSM23:KSM24 KIQ23:KIQ24 JYU23:JYU24 JOY23:JOY24 JFC23:JFC24 IVG23:IVG24 ILK23:ILK24 IBO23:IBO24 HRS23:HRS24 HHW23:HHW24 GYA23:GYA24 GOE23:GOE24 GEI23:GEI24 FUM23:FUM24 FKQ23:FKQ24 FAU23:FAU24 EQY23:EQY24 EHC23:EHC24 DXG23:DXG24 DNK23:DNK24 DDO23:DDO24 CTS23:CTS24 CJW23:CJW24 CAA23:CAA24 BQE23:BQE24 BGI23:BGI24 AWM23:AWM24 AMQ23:AMQ24 ACU23:ACU24 SY23:SY24 JC23:JC24 WVO27 WLS27 WBW27 VSA27 VIE27 UYI27 UOM27 UEQ27 TUU27 TKY27 TBC27 SRG27 SHK27 RXO27 RNS27 RDW27 QUA27 QKE27 QAI27 PQM27 PGQ27 OWU27 OMY27 ODC27 NTG27 NJK27 MZO27 MPS27 MFW27 LWA27 LME27 LCI27 KSM27 KIQ27 JYU27 JOY27 JFC27 IVG27 ILK27 IBO27 HRS27 HHW27 GYA27 GOE27 GEI27 FUM27 FKQ27 FAU27 EQY27 EHC27 DXG27 DNK27 DDO27 CTS27 CJW27 CAA27 BQE27 BGI27 AWM27 AMQ27 ACU27 SY27 JC27 WVO1:WVO10 JC1:JC10 SY1:SY10 ACU1:ACU10 AMQ1:AMQ10 AWM1:AWM10 BGI1:BGI10 BQE1:BQE10 CAA1:CAA10 CJW1:CJW10 CTS1:CTS10 DDO1:DDO10 DNK1:DNK10 DXG1:DXG10 EHC1:EHC10 EQY1:EQY10 FAU1:FAU10 FKQ1:FKQ10 FUM1:FUM10 GEI1:GEI10 GOE1:GOE10 GYA1:GYA10 HHW1:HHW10 HRS1:HRS10 IBO1:IBO10 ILK1:ILK10 IVG1:IVG10 JFC1:JFC10 JOY1:JOY10 JYU1:JYU10 KIQ1:KIQ10 KSM1:KSM10 LCI1:LCI10 LME1:LME10 LWA1:LWA10 MFW1:MFW10 MPS1:MPS10 MZO1:MZO10 NJK1:NJK10 NTG1:NTG10 ODC1:ODC10 OMY1:OMY10 OWU1:OWU10 PGQ1:PGQ10 PQM1:PQM10 QAI1:QAI10 QKE1:QKE10 QUA1:QUA10 RDW1:RDW10 RNS1:RNS10 RXO1:RXO10 SHK1:SHK10 SRG1:SRG10 TBC1:TBC10 TKY1:TKY10 TUU1:TUU10 UEQ1:UEQ10 UOM1:UOM10 UYI1:UYI10 VIE1:VIE10 VSA1:VSA10 WBW1:WBW10 WLS1:WLS10 H1:H28 WVO23:WVO24" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"params,data,json"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="E2:E27" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="E2:E28" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"P1,P2,P3,P4,P5"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D20" r:id="rId1" display="http://trade.qy-test.zszc.jianshicha.cn/etbApi/etbtrade/tenderFile/${tfId}" xr:uid="{276726E7-1E7B-434E-A24D-31E52B5478E2}"/>
-    <hyperlink ref="D24" r:id="rId2" display="http://trade.qy-test.zszc.jianshicha.cn/etbApi/etbtrade/tenderFile/${tfid}" xr:uid="{D0C8C29E-9E64-154A-86F9-7369B5B6C0E4}"/>
+    <hyperlink ref="D25" r:id="rId2" display="http://trade.qy-test.zszc.jianshicha.cn/etbApi/etbtrade/tenderFile/${tfid}" xr:uid="{D0C8C29E-9E64-154A-86F9-7369B5B6C0E4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
@@ -2987,19 +3132,19 @@
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="E2:E27">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3795,19 +3940,19 @@
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="E2:E24">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/env_test/case_excle/GovermentPurcharsWT/case_data_zz.xlsx
+++ b/data/env_test/case_excle/GovermentPurcharsWT/case_data_zz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Lucas/PycharmProjects/InterfaceAutomaticTesttPlatform/data/env_test/case_excle/GovermentPurcharsWT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBC68DB-F7E1-E145-98E3-250BC5688A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA6111C1-FAF9-C648-995E-25C26847D464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="19380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="19380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="公开" sheetId="10" r:id="rId1"/>
@@ -548,10 +548,6 @@
     <t>b26</t>
   </si>
   <si>
-    <t>{"scaleProcess":2,"ifOfferRank":"false","ifWeight":"false","ifCreditScore":"false","scorePrincipleType":0,"reviewer":"1","methodName":"0","ifCreditWeight":"false","ifSupportPreviewSumScore":"true","scorePrincipleParam":"{\"ruleContent\":\"汇总全部评分后，计算评分均值\"}","creditScoreParam":"{}","tfId":"${tfId}","steps":[{"ifPqr":"true","ifSummarize":"false","ifReject":"false","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"资格评审","sort":1,"stepType":0,"items":[{"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"rejectCondition\":{\"ruleContent\":\"当不满足条款数据大于等于1时，并且被评委否决人数大于等于1名时，否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":null,\"rank\":null},\"rejectType\":1}"},{"ifPqr":"false","ifSummarize":0,"ifReject":"true","ifBlindBid":"true","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"技术审查","sort":2,"stepType":1,"items":[{"itemMinScore":11,"itemMaxScore":70,"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"weight\":100,\"standardScore\":70,\"ifSummarize\":0,\"rejectCondition\":{\"ruleContent\":\"汇总得分至少为30分，否则否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":30,\"rank\":null},\"rejectType\":1,\"ifReject\":1}","standardScore":70,"catalogId":""},{"ifPqr":"false","ifSummarize":"false","ifReject":"true","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"报价得分","sort":3,"stepType":2,"standardScore":30,"catalogId":"${catalogId}","stepParam":"{\"weight\":100,\"standardScore\":30,\"catalogId\":\"1887306232988766210\",\"ifOpenComputeChange\":0,\"standardPriceRule\":{\"computeMode\":2,\"computeFunType\":1,\"ruleContent\":\"系统将使用有效投标单位投标报价最低的报价为基准价。\"},\"quotationScoreRule\":{\"deductPointByHigh\":3,\"deductPointByLow\":3,\"deductPointTo\":0,\"computeFunType\":3,\"ruleContent\":\"以基准值为最高分Fmax，报价每高于基准报价1%时扣3分，报价每低于基准报价1%扣3分，最低扣至0分\"}}"}],"resultGatherModeParam":"{\"type\":1,\"recCandidateNum\":3,\"ruleContent\":\"以汇总得分由高到低依次推荐3名中标候选人。汇总得分相等时，投标报价低的优先；投标报价也相等的，技术得分高的优先；当技术得分也相等的，排名相同，最终汇总得分排名第一的确定为中标人。\"}","resultGatherModeDesc":"汇总得分 =  价格得分"}</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>etbtrade/tpPurchaseGov?submit=true</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -663,6 +659,10 @@
   </si>
   <si>
     <t>a27</t>
+  </si>
+  <si>
+    <t>{"scaleProcess":2,"ifOfferRank":"false","ifWeight":"false","ifCreditScore":"false","scorePrincipleType":0,"reviewer":"1","methodName":"0","ifCreditWeight":"false","ifSupportPreviewSumScore":"true","scorePrincipleParam":"{\"ruleContent\":\"汇总全部评分后，计算评分均值\"}","creditScoreParam":"{}","tfId":"${tfId}","steps":[{"ifPqr":"true","ifSummarize":"false","ifReject":"false","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"资格评审","sort":1,"stepType":0,"items":[{"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"rejectCondition\":{\"ruleContent\":\"当不满足条款数据大于等于1时，并且被评委否决人数大于等于1名时，否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":null,\"rank\":null},\"rejectType\":1}"},{"ifPqr":"false","ifSummarize":0,"ifReject":"true","ifBlindBid":"true","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"技术审查","sort":2,"stepType":1,"items":[{"itemMinScore":11,"itemMaxScore":70,"itemName":"测试","itemStandard":"测试"}],"stepParam":"{\"weight\":100,\"standardScore\":70,\"ifSummarize\":0,\"rejectCondition\":{\"ruleContent\":\"汇总得分至少为30分，否则否决投标人。\",\"unSatisfiedNum\":1,\"rejectNum\":1,\"investment\":null,\"creditScore\":null,\"bidderNum\":null,\"totalScore\":30,\"rank\":null},\"rejectType\":1,\"ifReject\":1}","standardScore":70,"catalogId":""},{"ifPqr":"false","ifSummarize":"false","ifReject":"true","ifBlindBid":"false","rejectType":1,"ifOpenComputeChange":"false","isExpand":"false","stepName":"报价得分","sort":3,"stepType":2,"standardScore":30,"catalogId":"${catalogId}","stepParam":"{\"weight\":100,\"standardScore\":30,\"catalogId\":\"${catalogId}\",\"ifOpenComputeChange\":0,\"standardPriceRule\":{\"computeMode\":2,\"computeFunType\":1,\"ruleContent\":\"系统将使用有效投标单位投标报价最低的报价为基准价。\"},\"quotationScoreRule\":{\"deductPointByHigh\":3,\"deductPointByLow\":3,\"deductPointTo\":0,\"computeFunType\":3,\"ruleContent\":\"以基准值为最高分Fmax，报价每高于基准报价1%时扣3分，报价每低于基准报价1%扣3分，最低扣至0分\"}}"}],"resultGatherModeParam":"{\"type\":1,\"recCandidateNum\":3,\"ruleContent\":\"以汇总得分由高到低依次推荐3名中标候选人。汇总得分相等时，投标报价低的优先；投标报价也相等的，技术得分高的优先；当技术得分也相等的，排名相同，最终汇总得分排名第一的确定为中标人。\"}","resultGatherModeDesc":"汇总得分 =  价格得分"}</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -810,58 +810,7 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFD84472"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC80000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C6500"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC4E59F"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B853"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <font>
         <b/>
@@ -1411,13 +1360,13 @@
         <v>19</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>161</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>162</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>15</v>
@@ -1432,10 +1381,10 @@
         <v>43</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
@@ -1443,13 +1392,13 @@
         <v>61</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>163</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>164</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>15</v>
@@ -1464,10 +1413,10 @@
         <v>43</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="94.5" customHeight="1">
@@ -1475,13 +1424,13 @@
         <v>62</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>166</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>15</v>
@@ -1493,13 +1442,13 @@
         <v>17</v>
       </c>
       <c r="J5" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="K5" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="K5" s="10" t="s">
-        <v>169</v>
-      </c>
       <c r="M5" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
@@ -1510,10 +1459,10 @@
         <v>56</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>15</v>
@@ -1525,7 +1474,7 @@
         <v>17</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M6" s="5" t="s">
         <v>46</v>
@@ -1542,10 +1491,10 @@
         <v>57</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>15</v>
@@ -1632,10 +1581,10 @@
         <v>44</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>15</v>
@@ -1664,7 +1613,7 @@
         <v>26</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>55</v>
@@ -1697,7 +1646,7 @@
         <v>109</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>71</v>
@@ -1728,7 +1677,7 @@
         <v>105</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>112</v>
@@ -1762,7 +1711,7 @@
         <v>29</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>70</v>
@@ -1791,7 +1740,7 @@
         <v>93</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>76</v>
@@ -1826,7 +1775,7 @@
         <v>32</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>77</v>
@@ -1855,7 +1804,7 @@
         <v>79</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>34</v>
@@ -1884,7 +1833,7 @@
         <v>81</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>82</v>
@@ -1913,7 +1862,7 @@
         <v>83</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>88</v>
@@ -1942,7 +1891,7 @@
         <v>84</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>94</v>
@@ -1965,13 +1914,13 @@
     </row>
     <row r="21" spans="1:14" ht="90">
       <c r="A21" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>89</v>
@@ -2000,7 +1949,7 @@
         <v>86</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>90</v>
@@ -2055,13 +2004,13 @@
         <v>111</v>
       </c>
       <c r="B24" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>15</v>
@@ -2077,7 +2026,7 @@
         <v>43</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M24" s="5" t="s">
         <v>21</v>
@@ -2091,7 +2040,7 @@
         <v>47</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>101</v>
@@ -2106,7 +2055,7 @@
         <v>17</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>21</v>
@@ -2114,13 +2063,13 @@
     </row>
     <row r="26" spans="1:14" ht="90">
       <c r="A26" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>107</v>
@@ -2149,7 +2098,7 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="102.75" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>102</v>
@@ -2181,13 +2130,13 @@
     </row>
     <row r="28" spans="1:14" ht="90">
       <c r="A28" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>104</v>
@@ -2210,37 +2159,20 @@
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="E2:E23 E25:E28">
-    <cfRule type="cellIs" dxfId="19" priority="11" operator="equal">
+  <conditionalFormatting sqref="E2:E28">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="15" operator="equal">
-      <formula>"P1"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E24">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
-      <formula>"P5"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
-      <formula>"P4"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"P3"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
-      <formula>"P2"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2371,7 +2303,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>15</v>
@@ -2383,7 +2315,7 @@
         <v>17</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>46</v>
@@ -2403,7 +2335,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>15</v>
@@ -2493,7 +2425,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>15</v>
@@ -3027,7 +2959,7 @@
         <v>17</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M24" s="5" t="s">
         <v>21</v>
@@ -3132,19 +3064,19 @@
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="E2:E27">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3275,7 +3207,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>15</v>
@@ -3287,7 +3219,7 @@
         <v>17</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>46</v>
@@ -3307,7 +3239,7 @@
         <v>20</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>15</v>
@@ -3397,7 +3329,7 @@
         <v>20</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>15</v>
@@ -3538,8 +3470,8 @@
       <c r="H11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>153</v>
+      <c r="J11" s="10" t="s">
+        <v>183</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>21</v>
@@ -3835,7 +3767,7 @@
         <v>17</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M21" s="5" t="s">
         <v>21</v>
@@ -3940,19 +3872,19 @@
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="E2:E24">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"P5"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"P4"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"P3"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"P2"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"P1"</formula>
     </cfRule>
   </conditionalFormatting>
